--- a/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,18</t>
+          <t>-2,33; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,38</t>
+          <t>-1,59; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,0</t>
+          <t>-7,05; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,58</t>
+          <t>-1,0; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,81</t>
+          <t>-2,02; 0,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,21</t>
+          <t>-0,8; 1,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,21</t>
+          <t>-2,51; 0,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,57</t>
+          <t>-0,44; 0,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,45</t>
+          <t>-0,27; 0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,29</t>
+          <t>-0,76; 0,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 155,92</t>
+          <t>-90,03; 218,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,18</t>
+          <t>-1,99; 1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,12</t>
+          <t>-1,62; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,0</t>
+          <t>-6,98; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,6</t>
+          <t>-1,01; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,82</t>
+          <t>-1,98; 0,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,24</t>
+          <t>-2,53; 0,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,48</t>
+          <t>-0,38; 0,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,52</t>
+          <t>-0,27; 0,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,32</t>
+          <t>-0,69; 0,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-90,03; 218,97</t>
+          <t>-89,38; 177,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,19</t>
+          <t>-2,02; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,19</t>
+          <t>-1,59; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,0</t>
+          <t>-6,4; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,63</t>
+          <t>-1,0; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,82</t>
+          <t>-1,95; 0,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,22</t>
+          <t>-0,8; 1,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,27</t>
+          <t>-2,55; 0,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,48</t>
+          <t>-0,38; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,49</t>
+          <t>-0,29; 0,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,3</t>
+          <t>-0,85; 0,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-89,38; 177,64</t>
+          <t>-89,42; 155,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,20 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8311982221318823</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +624,104 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,77</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>4.768272556961131</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-10,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 1,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.6224529554135814</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.06943422497793628</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-0.1067539157482476</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>-2.017499843108796</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.529793840361162</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>1.184350556098998</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +729,117 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,47</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,59; 3,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5694759568485364</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.193104707428763</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2433911554342847</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.593005100558009</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,29</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 0,0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>3.471935365201828</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.377357489012003</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +847,323 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 1,58</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 0,0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-48,81%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-71,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 0,81</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 1,21</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-2,55; 0,21</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.239060993548889</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-1.276319764459287</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-36,68%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-6.396778701398269</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 0,57</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 0,45</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,85; 0,29</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-89,42; 155,92</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>6.290237512003406</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.02358613828598042</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.4608097652070892</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.04713506664224163</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.004139857681923</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.200405725674119</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.579762689530513</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-0.3875992254831573</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.004828958133275187</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-0.7466602144784205</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4881372030545469</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.01218414057617009</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.7190960108689887</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-1.948888294784838</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-0.79969385177354</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-2.553393028737337</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.8077640557796756</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1.210273471367149</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.2119364548883413</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.01184915717661484</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.07371427667765011</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.1906743899946088</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.04321684935985642</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.4083414712512592</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-0.3667640239324016</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-0.3816091630750985</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.2881621019505266</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.8520872983028357</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="n">
+        <v>-0.8941683134472348</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.566300157448568</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.4501799136131918</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.2857973357851848</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="n">
+        <v>1.559219365753002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1172,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
